--- a/checklist_forms/012_regulatory_record_archival_checklist--checklist_forms.xlsx
+++ b/checklist_forms/012_regulatory_record_archival_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,46 +515,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_header</t>
+          <t>regulatory_record_type</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>form_header</t>
+          <t>What type of regulatory record is being archived?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>regulatory_body</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>regulatory_body</t>
+          <t>Which department is responsible for the record?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,36 +571,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>date_of_archival</t>
+          <t>What is the date of archival?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>current_location</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>What is the current location of the record?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>file_upload</t>
+          <t>reviewed_and_approved</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>file_upload</t>
+          <t>Has the record been properly reviewed and approved?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,64 +635,64 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>regulatory_body</t>
+          <t>up_to_date</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>regulatory_body</t>
+          <t>Is the record up-to-date and current?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>date_of_archival</t>
+          <t>reason_for_archival</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>date_of_archival</t>
+          <t>What is the reason for archival?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>associated_documents</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>Are there any associated documents or files that need to be stored with the record?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>file_upload</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,62 +727,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>regulatory_body</t>
+          <t>file_upload_details</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>regulatory_body</t>
+          <t>File Upload Details</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>date_of_archival</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>date_of_archival</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>department</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>department</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -799,10 +753,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -827,51 +781,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>regulatory_record_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>department_1</t>
+          <t>record_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Department 1</t>
+          <t>Record 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>regulatory_record_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>department_2</t>
+          <t>record_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Department 2</t>
+          <t>Record 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>regulatory_record_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>department_3</t>
+          <t>record_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Department 3</t>
+          <t>Record 3</t>
         </is>
       </c>
     </row>
@@ -921,57 +875,6 @@
         </is>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t>Department 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>department_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>department_1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Department 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>department_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>department_2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Department 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>department_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>department_3</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
         <is>
           <t>Department 3</t>
         </is>
